--- a/backend tests.xlsx
+++ b/backend tests.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="328">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -58,7 +58,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -68,7 +68,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
@@ -78,7 +78,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -226,7 +226,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -236,7 +236,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
@@ -246,7 +246,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -802,6 +802,267 @@
   </si>
   <si>
     <t xml:space="preserve">T-54,T-55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_user_state_admin works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/update_user_state_admin/ with the body {  "admin_id": "&lt;b64 encoded admin user id&gt;",  "admin_session_token": "&lt;b64 encoded admin session token&gt;"   "target_user_id":"&lt;b64 enc. id of targed user&gt;",  "new_user_state":"&lt;b64 enc. desired user state&gt;",  "reason":"&lt;b64 enc. ban reason ! only if the new user state is banned !&gt;"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-58,T-59,T-60,T-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_user_state_admin works (wrong permissions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/update_user_state_admin/ with the body {  "admin_id": "&lt;b64 encoded NON ADMIN id&gt;",  "admin_session_token": "&lt;b64 encoded NON ADMIN session token&gt;"   "target_user_id":"&lt;b64 enc. id of targed user&gt;",  "new_user_state":"&lt;b64 enc. desired user state&gt;",  "reason":"&lt;b64 enc. ban reason ! only if the new user state is banned !&gt;"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 403 (FORBIDDEN), body: „{     "status": "permission_denied",     "statuscode": "403" }"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-57,T-59,T-60,T-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_user_state_admin works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/update_user_state_admin/ with the body {  "admin_id": "&lt;b64 encoded admin id&gt;",  "admin_session_token": "&lt;b64 encoded WRONG admin session token&gt;"   "target_user_id":"&lt;b64 enc. id of targed user&gt;",  "new_user_state":"&lt;b64 enc. desired user state&gt;",  "reason":"&lt;b64 enc. ban reason ! only if the new user state is banned !&gt;"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 401 (UNATHORIZED), body: „{     "status": "incorrect_credentials",     "statuscode": "401" }"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-57,T-58,T-60,T-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_user_state_admin works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/update_user_state_admin/ with the body {  "admin_id": "&lt;b64 encoded admin id&gt;",  "admin_session_token": "&lt;b64 encoded admin session token&gt;"   "target_user_id":"&lt;b64 enc. id of targed user&gt;",  "new_user_state":"&lt;b64 enc. desired user state&gt;",  "reason":"&lt;b64 enc. ban reason ! only if the new user state is banned !&gt;"}, without an auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 401 (UNATHORIZED), body: „{"status":"missing_auth_header","statuscode":"401"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-57,T-58,T-59,T-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_user_state_admin works (missing fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/update_user_state_admin/ with the body {  "admin_id": "&lt;b64 encoded admin id&gt;",  "admin_session_token": "&lt;b64 encoded admin session token&gt;"   "target_user_id":"&lt;b64 enc. id of targed user&gt;",  "reason":"&lt;b64 enc. ban reason ! only if the new user state is banned !&gt;"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-57,T-58,T-59,T-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_product works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  "admin_id": "&lt;b64 encoded admin user {   "user_id": "&lt;base64 enc. id of admin&gt;",    "session_token": "&lt;base64 enc. session token of admin&gt;",    "name_de":"&lt;b64 enc. string&gt;",    "description_en":"&lt;b64 enc. string&gt;",    "price_huf":"&lt;b64 enc. int&gt;",   "times_ordered":"&lt;b64 enc. int&gt;",    "stock":"&lt;b64 enc. int&gt;",   "sale_percentage":"&lt;b64 enc. int&gt;",    "description_preview_en":"&lt;b64 enc. string&gt;",     "name_hu":"&lt;b64 enc. string&gt;",     "name_en":"&lt;b64 enc. string&gt;",    "description_hu":"&lt;b64 enc. string&gt;",    "description_de":"&lt;b64 enc. string&gt;",     "description_preview_hu":"&lt;b64 enc. string&gt;",    "description_preview_de":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",  "manufacturer":"&lt;b64 enc. string&gt;",   "brand":"&lt;b64 enc. string&gt;",  "rating":"&lt;b64 enc. int&gt;",  "sku":"&lt;b64 enc. string&gt;",   "active_ingredients":"&lt;b64 enc. string&gt;",   "packaging_en":"&lt;b64 enc. string&gt;",   "packaging_hu":"&lt;b64 enc. string&gt;",  "packaging_de":"&lt;b64 enc. string&gt;",  "thumbnail_url":"&lt;b64 enc. string&gt;", "featured":"&lt;b64 enc. Int&gt;"  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-64, T-65, T-65, T-66, T-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_product works (not admin user)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  "admin_id": "&lt;b64 encoded admin user {   "user_id": "&lt;base64 encNOT . id of admin&gt;",    "session_token": "&lt;base64 enc. session token of admin&gt;",    "name_de":"&lt;b64 enc. Strina NOT g&gt;",  user   "description_en":"&lt;b64 enc. string&gt;",    "price_huf":"&lt;b64 enc. int&gt;",   "times_ordered":"&lt;b64 enc. int&gt;",    "stock":"&lt;b64 enc. int&gt;",   "sale_percentage":"&lt;b64 enc. int&gt;",    "description_preview_en":"&lt;b64 enc. string&gt;",     "name_hu":"&lt;b64 enc. string&gt;",     "name_en":"&lt;b64 enc. string&gt;",    "description_hu":"&lt;b64 enc. string&gt;",    "description_de":"&lt;b64 enc. string&gt;",     "description_preview_hu":"&lt;b64 enc. string&gt;",    "description_preview_de":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",  "manufacturer":"&lt;b64 enc. string&gt;",   "brand":"&lt;b64 enc. string&gt;",  "rating":"&lt;b64 enc. int&gt;",  "sku":"&lt;b64 enc. string&gt;",   "active_ingredients":"&lt;b64 enc. string&gt;",   "packaging_en":"&lt;b64 enc. string&gt;",   "packaging_hu":"&lt;b64 enc. string&gt;",  "packaging_de":"&lt;b64 enc. string&gt;",  "thumbnail_url":"&lt;b64 enc. string&gt;", "featured":"&lt;b64 enc. Int&gt;"  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-62, T-64, T-65, T-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_product works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  "admin_id": "&lt;b64 encoded admin user {   "user_id": "&lt;base64 enc. id of admin&gt;",    "session_token": "&lt;base64 enc. INCORRECT session token of admin&gt;",    "name_de":"&lt;b64 enc. string&gt;",    "description_en":"&lt;b64 enc. string&gt;",    "price_huf":"&lt;b64 enc. int&gt;",   "times_ordered":"&lt;b64 enc. int&gt;",    "stock":"&lt;b64 enc. int&gt;",   "sale_percentage":"&lt;b64 enc. int&gt;",    "description_preview_en":"&lt;b64 enc. string&gt;",     "name_hu":"&lt;b64 enc. string&gt;",     "name_en":"&lt;b64 enc. string&gt;",    "description_hu":"&lt;b64 enc. string&gt;",    "description_de":"&lt;b64 enc. string&gt;",     "description_preview_hu":"&lt;b64 enc. string&gt;",    "description_preview_de":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",  "manufacturer":"&lt;b64 enc. string&gt;",   "brand":"&lt;b64 enc. string&gt;",  "rating":"&lt;b64 enc. int&gt;",  "sku":"&lt;b64 enc. string&gt;",   "active_ingredients":"&lt;b64 enc. string&gt;",   "packaging_en":"&lt;b64 enc. string&gt;",   "packaging_hu":"&lt;b64 enc. string&gt;",  "packaging_de":"&lt;b64 enc. string&gt;",  "thumbnail_url":"&lt;b64 enc. string&gt;", "featured":"&lt;b64 enc. Int&gt;"  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-62, T-63, T-65, T-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_product works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  "admin_id": "&lt;b64 encoded admin user {   "user_id": "&lt;base64 enc. id of admin&gt;",    "session_token": "&lt;base64 enc. session token of admin&gt;",    "name_de":"&lt;b64 enc. string&gt;",    "description_en":"&lt;b64 enc. string&gt;",    "price_huf":"&lt;b64 enc. int&gt;",   "times_ordered":"&lt;b64 enc. int&gt;",    "stock":"&lt;b64 enc. int&gt;",   "sale_percentage":"&lt;b64 enc. int&gt;",    "description_preview_en":"&lt;b64 enc. string&gt;",     "name_hu":"&lt;b64 enc. string&gt;",     "name_en":"&lt;b64 enc. string&gt;",    "description_hu":"&lt;b64 enc. string&gt;",    "description_de":"&lt;b64 enc. string&gt;",     "description_preview_hu":"&lt;b64 enc. string&gt;",    "description_preview_de":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",  "manufacturer":"&lt;b64 enc. string&gt;",   "brand":"&lt;b64 enc. string&gt;",  "rating":"&lt;b64 enc. int&gt;",  "sku":"&lt;b64 enc. string&gt;",   "active_ingredients":"&lt;b64 enc. string&gt;",   "packaging_en":"&lt;b64 enc. string&gt;",   "packaging_hu":"&lt;b64 enc. string&gt;",  "packaging_de":"&lt;b64 enc. string&gt;",  "thumbnail_url":"&lt;b64 enc. string&gt;", "featured":"&lt;b64 enc. Int&gt;"  }, and no header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-62, T-63, T-64, T-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_product works (missing fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  "admin_id": "&lt;b64 encoded admin user {   "user_id": "&lt;base64 enc. id of admin&gt;",    "session_token": "&lt;base64 enc. session token of admin&gt;",    "name_de":"&lt;b64 enc. string&gt;",    "description_en":"&lt;b64 enc. string&gt;",    "price_huf":"&lt;b64 enc. int&gt;",   "times_ordered":"&lt;b64 enc. int&gt;",    "stock":"&lt;b64 enc. int&gt;",   "sale_percentage":"&lt;b64 enc. int&gt;",    "description_preview_en":"&lt;b64 enc. string&gt;",     "name_hu":"&lt;b64 enc. string&gt;",     "name_en":"&lt;b64 enc. string&gt;",    "description_hu":"&lt;b64 enc. string&gt;",    "description_de":"&lt;b64 enc. string&gt;",     "description_preview_hu":"&lt;b64 enc. string&gt;",    "description_preview_de":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",  "manufacturer":"&lt;b64 enc. string&gt;",   "brand":"&lt;b64 enc. string&gt;",  "rating":"&lt;b64 enc. int&gt;",  "sku":"&lt;b64 enc. string&gt;",   "active_ingredients":"&lt;b64 enc. string&gt;",   "packaging_en":"&lt;b64 enc. String&gt;"  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-62, T-63, T-64, T-65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_order works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_order with the body {   "order": {     "user_id": "&lt;b64 enc. id of user&gt;",     "session_token": "&lt;b64 enc.  Session token of user&gt;",     "email": "&lt;b64 enc. email of user&gt;",     "billing_name": "&lt;64 enc. string&gt;",     "shipping_name": "&lt;64 enc. string&gt;",     "shipping_company": "&lt;64 enc. string&gt;",     "price": "&lt;64 enc. int&gt;",     "city": "&lt;64 enc. string&gt;",     "guest": "&lt;64 enc. int (0,1)&gt;",     "zipcode": "&lt;64 enc. int&gt;",     "address": "&lt;64 enc. string&gt;",     "apartment_number": "&lt;64 enc. int&gt;",     "note": "&lt;64 enc. string&gt;",     "house_number": "&lt;64 enc. int&gt;",     "phone_number": "&lt;64 enc. string&gt;"   },   "items": [     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"         },     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"           }   ] }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{"status":"success","statuscode":"200","tracking_token":"&lt;the order’s tracking token&gt;"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-68,T-69,T-70,T-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_order works (banned user)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_order with the body {   "order": {     "user_id": "&lt;b64 enc. id of a BANNED user&gt;",     "session_token": "&lt;b64 enc.  Session token of user&gt;",     "email": "&lt;b64 enc. email of user&gt;",     "billing_name": "&lt;64 enc. string&gt;",     "shipping_name": "&lt;64 enc. string&gt;",     "shipping_company": "&lt;64 enc. string&gt;",     "price": "&lt;64 enc. int&gt;",     "city": "&lt;64 enc. string&gt;",     "guest": "&lt;64 enc. int (0,1)&gt;",     "zipcode": "&lt;64 enc. int&gt;",     "address": "&lt;64 enc. string&gt;",     "apartment_number": "&lt;64 enc. int&gt;",     "note": "&lt;64 enc. string&gt;",     "house_number": "&lt;64 enc. int&gt;",     "phone_number": "&lt;64 enc. string&gt;"   },   "items": [     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"         },     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"           }   ] }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 403 (FORBIDDEN), body: „{"status":"permission_denied","statuscode":"403"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-67,T-69,T-70,T-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_order works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_order with the body {   "order": {     "user_id": "&lt;b64 enc. id of user&gt;",     "session_token": "&lt;b64 enc. INCORRECT Session token of user&gt;",     "email": "&lt;b64 enc. email of user&gt;",     "billing_name": "&lt;64 enc. string&gt;",     "shipping_name": "&lt;64 enc. string&gt;",     "shipping_company": "&lt;64 enc. string&gt;",     "price": "&lt;64 enc. int&gt;",     "city": "&lt;64 enc. string&gt;",     "guest": "&lt;64 enc. int (0,1)&gt;",     "zipcode": "&lt;64 enc. int&gt;",     "address": "&lt;64 enc. string&gt;",     "apartment_number": "&lt;64 enc. int&gt;",     "note": "&lt;64 enc. string&gt;",     "house_number": "&lt;64 enc. int&gt;",     "phone_number": "&lt;64 enc. string&gt;"   },   "items": [     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"         },     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"           }   ] }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 401 (UNATHORIZED), body: „{"status":"incorrect_credentials","statuscode":"401"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-67,T-68,T-70,T-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_order works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_order with the body {   "order": {     "user_id": "&lt;b64 enc. id of user&gt;",     "session_token": "&lt;b64 enc.  Session token of user&gt;",     "email": "&lt;b64 enc. email of user&gt;",     "billing_name": "&lt;64 enc. string&gt;",     "shipping_name": "&lt;64 enc. string&gt;",     "shipping_company": "&lt;64 enc. string&gt;",     "price": "&lt;64 enc. int&gt;",     "city": "&lt;64 enc. string&gt;",     "guest": "&lt;64 enc. int (0,1)&gt;",     "zipcode": "&lt;64 enc. int&gt;",     "address": "&lt;64 enc. string&gt;",     "apartment_number": "&lt;64 enc. int&gt;",     "note": "&lt;64 enc. string&gt;",     "house_number": "&lt;64 enc. int&gt;",     "phone_number": "&lt;64 enc. string&gt;"   },   "items": [     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"         },     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. Int&gt;"           }   ] }, and no header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-67,T-68,T-69,T-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_order works (missing fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_order with the body {   "order": {     "user_id": "&lt;b64 enc. id of user&gt;",     "session_token": "&lt;b64 enc.  Session token of user&gt;",     "email": "&lt;b64 enc. email of user&gt;",     "billing_name": "&lt;64 enc. string&gt;",     "shipping_name": "&lt;64 enc. string&gt;",     "shipping_company": "&lt;64 enc. string&gt;",     "price": "&lt;64 enc. int&gt;",     "city": "&lt;64 enc. String&gt;",    "address": "&lt;64 enc. string&gt;",     "apartment_number": "&lt;64 enc. int&gt;",     "note": "&lt;64 enc. string&gt;",     "house_number": "&lt;64 enc. int&gt;",     "phone_number": "&lt;64 enc. string&gt;"   },   "items": [     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"         },     {       "product_id": "&lt;64 enc. int&gt;",       "quantity": "&lt;64 enc. int&gt;"           }   ] }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-67,T-68,T-69,T-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_post works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of admin&gt;",   "session_token": ""&lt;b64 enc. session token of admin&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. int&gt;",    "is_featured":"&lt;b64 enc. int (0,1)&gt;",    "tags":"&lt;b64 enc. string&gt;" }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{"status":"success","statuscode":"200"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-73,T-74,T-75,T-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_post works (missing admin priviliges)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of NON-ADMIN user&gt;",   "session_token": ""&lt;b64 enc. session token of NON-ADMIN user&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. int&gt;",    "is_featured":"&lt;b64 enc. int (0,1)&gt;",    "tags":"&lt;b64 enc. string&gt;" }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-72,T-74,T-75,T-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_post works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of admin&gt;",   "session_token": ""&lt;b64 enc. INCORRECT session token of admin&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. int&gt;",    "is_featured":"&lt;b64 enc. int (0,1)&gt;",    "tags":"&lt;b64 enc. string&gt;" }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-73,T-72,T-75,T-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_post works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of admin&gt;",   "session_token": ""&lt;b64 enc. session token of admin&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. int&gt;",    "is_featured":"&lt;b64 enc. int (0,1)&gt;",    "tags":"&lt;b64 enc. String&gt;" }, and no auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-73,T-74,T-72,T-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/create_post works (missing fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of admin&gt;",   "session_token": ""&lt;b64 enc. session token of admin&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. Int&gt;" }   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-73,T-74,T-75,T-72</t>
   </si>
 </sst>
 </file>
@@ -813,7 +1074,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,31 +1102,24 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF81D41A"/>
-      <name val="DejaVu Sans"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -884,7 +1138,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF339966"/>
       </patternFill>
     </fill>
     <fill>
@@ -946,7 +1200,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -991,15 +1245,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1056,7 +1306,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC55A11"/>
@@ -1252,17 +1502,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="77.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="33.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.07"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.68"/>
   </cols>
@@ -2311,8 +2561,12 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="97.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
+      <c r="A37" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="C37" s="1" t="s">
         <v>25</v>
       </c>
@@ -3006,7 +3260,7 @@
       <c r="C61" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -3081,6 +3335,586 @@
       </c>
       <c r="I63" s="12" t="n">
         <v>46079</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>46104</v>
       </c>
     </row>
   </sheetData>
@@ -3089,6 +3923,16 @@
     <hyperlink ref="D51" r:id="rId2" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded id”, &quot;passwo"/>
     <hyperlink ref="D52" r:id="rId3" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ without a body or an s_featured"/>
     <hyperlink ref="D53" r:id="rId4" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded i” "/>
+    <hyperlink ref="D71" r:id="rId5" display="http://localhost:90/api/create_product/"/>
+    <hyperlink ref="D72" r:id="rId6" display="http://localhost:90/api/create_product/"/>
+    <hyperlink ref="D73" r:id="rId7" display="http://localhost:90/api/create_product/"/>
+    <hyperlink ref="D74" r:id="rId8" display="http://localhost:90/api/create_product/"/>
+    <hyperlink ref="D75" r:id="rId9" display="http://localhost:90/api/create_product/"/>
+    <hyperlink ref="D83" r:id="rId10" display="https://www.roysshack.hu/create_post"/>
+    <hyperlink ref="D84" r:id="rId11" display="https://www.roysshack.hu/create_post"/>
+    <hyperlink ref="D85" r:id="rId12" display="https://www.roysshack.hu/create_post"/>
+    <hyperlink ref="D86" r:id="rId13" display="https://www.roysshack.hu/create_post"/>
+    <hyperlink ref="D87" r:id="rId14" display="https://www.roysshack.hu/create_post"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/backend tests.xlsx
+++ b/backend tests.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="328">
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="419">
   <si>
     <t xml:space="preserve">Task ID</t>
   </si>
@@ -1020,7 +1017,7 @@
     <t xml:space="preserve">T-73</t>
   </si>
   <si>
-    <t xml:space="preserve">Test if api/create_post works (missing admin priviliges)</t>
+    <t xml:space="preserve">Test if api/create_post works (missing admin privileges)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   "user_id": "&lt;b64 enc. id of NON-ADMIN user&gt;",   "session_token": ""&lt;b64 enc. session token of NON-ADMIN user&gt;",   "title":""&lt;b64 enc. string&gt;",    "content":"&lt;b64 enc. string&gt;",    "image_url":"&lt;b64 enc. string&gt;",   "category_id":"&lt;b64 enc. int&gt;",   "slug":"&lt;b64 enc. string&gt;",   "except":"&lt;b64 enc. string&gt;",    "status":"&lt;b64 enc. string (hidden, draft, published, archived)&gt;",   "views":"&lt;b64 enc. int&gt;",    "likes":"&lt;b64 enc. int&gt;",   "comment_count":"&lt;b64 enc. int&gt;",    "is_featured":"&lt;b64 enc. int (0,1)&gt;",    "tags":"&lt;b64 enc. string&gt;" }   </t>
@@ -1063,6 +1060,282 @@
   </si>
   <si>
     <t xml:space="preserve">T-73,T-74,T-75,T-72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_user_state works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_user_state with the body{ "id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user” }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "status": "success",     "account_state": "admin",     "statuscode": "200" }"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78,T-79,T-80,T-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_user_state works (banned user)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "status": "success",     "account_state": "banned",     "statuscode": "200" }"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78,T-77,T-80,T-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_user_state works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_user_state with the body{ "id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. INCORRECT session token of user” }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78,T-80,T-77,T-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_user_state works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_user_state with the body{ "id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user” }, and no auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78,T-79,T-77,T-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_user_state works (missing fields)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_user_state with the body{ "id":"&lt;b64 enc. id of user&gt;"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-78,T-79,T-80,T-77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/increment_post_views_by_id works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/increment_post_views with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "status": "success",     "statuscode": "200" }”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83,T-84,T-85,T-86,T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/increment_post_views_by_id works (banned user)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{"status":"permission_denied","statuscode":"403"}”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-82,T-84,T-85,T-86,T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/increment_post_views_by_id works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/increment_post_views with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. INCORRECT session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 401 (UNATHORIZED), body: „{"status":"inexistent_user_or_incorrect_data","statuscode":"401"}"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83,T-82,T-85,T-86,T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/increment_post_views_by_id works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/increment_post_views with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }, and no auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83,T-84,T-82,T-86,T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/increment_post_views_by_id works (missing field)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/increment_post_views with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;" }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83,T-84,T-85,T-82,T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-83,T-82,T-85,T-86,T-84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_stock works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-89,T-90,T-91,T-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_stock works (missing admin privileges)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-88,T-90,T-91,T-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_stock works (wrong token)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. INCORRECT session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-88,T-89,T-91,T-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_stock works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;", "post_id":"&lt;b64 enc. id of post&gt;" }, and no auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-88,T-89,T-90,T-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/update_stock works (missing field)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  "user_id":"&lt;b64 enc. id of user&gt;", "session_token":"&lt;b64 enc. session token of user&gt;", "post_id":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-88,T-89,T-90,T-91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_post_by_id with the body {  "id":"&lt;b6 enc. Id of post&gt;", „admin”: „&lt;b64 encoded 0”  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "statuscode": "200",     "status": "success",     "post": {         "id": "&lt;id of post&gt;",         "title": "&lt;title of post&gt;",         "content": "&lt;icontentd of post&gt;",         "user_id": "&lt;user_id of post&gt;",         "created_at": "&lt;created_at date of post&gt;",         "image_url": "&lt;image_url of post&gt;",         "category_id": "&lt;category_id of post&gt;",         "updated_at": "&lt;updated_at date of post&gt;",         "slug": "&lt;slug of post&gt;",         "excerpt": "&lt;excerpt of post&gt;",         "status": "&lt;status of post&gt;",         "views": "&lt;views count of post&gt;",         "likes": "&lt;likes count of post&gt;",         "comment_count": "&lt;comment_count of post&gt;",         "is_featured": "&lt;is_featured (0/1) of post&gt;",         "published_at": "&lt;published_at date of post&gt;",         "last_activity_at": "&lt;last_activity_at date of post&gt;",         "tags": "&lt;tags of post&gt;"     } }”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-94,T-95,T-96,T-97,T-98,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works (wrong post id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_post_by_id with the body {  "id":"&lt;b6 enc. INCORRECT id of post&gt;", „admin”: „&lt;b64 encoded 0”  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "statuscode": "200",     "status": "success",     "post": {} }”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-95,T-96,T-97,T-98,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works (hidden post)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: 200 (SUCCESS), body: „{     "statuscode": "403",     "status": "permission_denied” }”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-94,T-96,T-97,T-98,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works (no jwt provided)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_post_by_id with the body {  "id":"&lt;b6 enc. Id of post&gt;", „admin”: „&lt;b64 encoded 0”  }, and no auth header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-94,T-95,T-97,T-98,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works (missing field)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_post_by_id with the body {  "id":"&lt;b6 enc. Id of post&gt;"  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-94,T-95,T-96,T-98,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-94,T-95,T-96,T-97,T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if api/get_post_by_id works (hidden post, admin user)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open postman 2. Send a request to https://www.roysshack.hu/get_post_by_id with the body {  "id":"&lt;b6 enc. Id of post&gt;", „admin”: „&lt;b64 encoded 1”, „admin_id”:”&lt;b64 enc. Id of admin”, „admin_session_token”: „&lt;b64 enc. Session token of admin&gt;”  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-93,T-94,T-95,T-96,T-97,T-98</t>
   </si>
 </sst>
 </file>
@@ -1502,32 +1775,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V87"/>
+  <dimension ref="A1:U1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="77.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="33.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="77.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="57.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="9" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="23" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1536,48 +1810,42 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="105.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="105.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="9" t="n">
+        <v>45978</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="81.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="9" t="n">
-        <v>45978</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="81.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -1589,21 +1857,18 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>45979</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -1615,24 +1880,21 @@
         <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="9" t="n">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>45979</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>24</v>
@@ -1644,24 +1906,21 @@
         <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="9" t="n">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>45979</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>29</v>
@@ -1673,24 +1932,21 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="9" t="n">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>45980</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -1699,27 +1955,24 @@
         <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="n">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>45980</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>38</v>
@@ -1731,24 +1984,21 @@
         <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="9" t="n">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>45982</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>43</v>
@@ -1756,25 +2006,22 @@
       <c r="C9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>45982</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>47</v>
@@ -1786,253 +2033,226 @@
         <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>45983</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>45983</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="E11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="9" t="n">
+        <v>46005</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="60.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>46005</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="60.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="9" t="n">
+        <v>46005</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>46005</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="9" t="n">
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>46006</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="1" t="s">
+    <row r="15" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>46006</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="9" t="n">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>46006</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="1" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="87.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="87.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>13</v>
-      </c>
       <c r="H17" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>80</v>
@@ -2040,25 +2260,22 @@
       <c r="C19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="10" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>84</v>
@@ -2066,29 +2283,26 @@
       <c r="C20" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="9" t="n">
+        <v>46034</v>
+      </c>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>46034</v>
-      </c>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>89</v>
@@ -2100,53 +2314,47 @@
         <v>91</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="1" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="E22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>98</v>
@@ -2158,27 +2366,24 @@
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>99</v>
@@ -2187,24 +2392,21 @@
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>13</v>
+        <v>100</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>106</v>
@@ -2216,24 +2418,21 @@
         <v>108</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="9" t="n">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>111</v>
@@ -2245,24 +2444,21 @@
         <v>113</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="9" t="n">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>116</v>
@@ -2274,24 +2470,21 @@
         <v>118</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>120</v>
@@ -2300,27 +2493,24 @@
         <v>121</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>123</v>
@@ -2332,24 +2522,21 @@
         <v>125</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>128</v>
@@ -2361,24 +2548,21 @@
         <v>130</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>133</v>
@@ -2386,53 +2570,48 @@
       <c r="C31" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="10" t="s">
         <v>135</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I31" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>32</v>
-      </c>
       <c r="B32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I32" s="9" t="n">
+      <c r="H32" s="9" t="n">
         <v>46065</v>
       </c>
+      <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
@@ -2445,11 +2624,10 @@
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="44.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>33</v>
+      <c r="A33" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>142</v>
@@ -2461,27 +2639,24 @@
         <v>144</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="144.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="144.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>146</v>
@@ -2490,27 +2665,24 @@
         <v>147</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="101.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="101.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>149</v>
+      <c r="B35" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>16</v>
@@ -2519,24 +2691,21 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="9" t="n">
         <v>46065</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="227.2" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>150</v>
+      <c r="A36" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>20</v>
@@ -2545,27 +2714,24 @@
         <v>21</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="9" t="n">
+      <c r="H36" s="9" t="n">
         <v>46065</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="97.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>150</v>
+      <c r="A37" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>25</v>
@@ -2574,719 +2740,644 @@
         <v>26</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="9" t="n">
+      <c r="H37" s="9" t="n">
         <v>45979</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="108.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="10" t="s">
+      <c r="A38" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>152</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="122.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="155.35" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="112.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="B41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="97.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="H42" s="9" t="n">
         <v>46065</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="122.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="10" t="s">
+    <row r="43" customFormat="false" ht="112.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" s="9" t="n">
+      <c r="B44" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="9" t="n">
         <v>46065</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="155.35" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="10" t="s">
+    <row r="45" customFormat="false" ht="87.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I40" s="9" t="n">
+      <c r="D46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="9" t="n">
         <v>46065</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="112.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="97.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="112.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="58.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="1" t="s">
+    <row r="47" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="87.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="72.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="n">
-        <v>40</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="10" t="s">
         <v>168</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="n">
-        <v>41</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="10" t="s">
         <v>172</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="9" t="n">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="G48" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H48" s="10"/>
-      <c r="I48" s="9" t="n">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="30.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10" t="n">
-        <v>42</v>
-      </c>
       <c r="B49" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="9" t="n">
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="9" t="n">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="n">
-        <v>43</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="10" t="s">
         <v>178</v>
       </c>
       <c r="E50" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="H50" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="n">
-        <v>44</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="n">
-        <v>45</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="10" t="s">
         <v>185</v>
       </c>
       <c r="E52" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="H52" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="n">
-        <v>46</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="10" t="s">
         <v>189</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="I53" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="n">
-        <v>47</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="10" t="s">
         <v>193</v>
       </c>
       <c r="E54" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="n">
-        <v>48</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="10" t="s">
         <v>198</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="B56" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="9" t="n">
         <v>46073</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56" s="1" t="s">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I56" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="1" t="s">
         <v>207</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>208</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="9" t="n">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="I57" s="9" t="n">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>213</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="12" t="n">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="1" t="s">
         <v>217</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>218</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="12" t="n">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="1" t="s">
         <v>222</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>223</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="12" t="n">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="1" t="s">
         <v>227</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="12" t="n">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3295,644 +3386,1212 @@
       <c r="E62" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="12" t="n">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="B63" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H63" s="12" t="n">
         <v>46079</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C63" s="10" t="s">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>247</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>252</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>257</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="B69" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H69" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" s="1" t="s">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="B71" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H71" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="1" t="s">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="B72" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H72" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" s="1" t="s">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I72" s="12" t="n">
+      <c r="B73" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="1" t="s">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="I73" s="12" t="n">
+      <c r="B74" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H74" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" s="1" t="s">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="B75" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H75" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H75" s="1" t="s">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="1" t="s">
         <v>285</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>286</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>291</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="I78" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C79" s="1" t="s">
         <v>295</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>296</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="B80" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H80" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="1" t="s">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="B81" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H81" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H81" s="1" t="s">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>309</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="12" t="n">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="B84" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H84" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="1" t="s">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="B85" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H85" s="1" t="s">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="I85" s="12" t="n">
+      <c r="B86" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H86" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" s="1" t="s">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="B87" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H87" s="12" t="n">
         <v>46104</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H87" s="1" t="s">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>46104</v>
-      </c>
-    </row>
+      <c r="B89" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0"/>
+      <c r="B101" s="0"/>
+      <c r="C101" s="0"/>
+      <c r="D101" s="0"/>
+      <c r="E101" s="0"/>
+      <c r="F101" s="0"/>
+      <c r="G101" s="0"/>
+      <c r="H101" s="0"/>
+      <c r="I101" s="0"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>46105</v>
+      </c>
+      <c r="I102" s="0"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>46105</v>
+      </c>
+      <c r="I103" s="0"/>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>46105</v>
+      </c>
+      <c r="I104" s="0"/>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B107" s="10"/>
+      <c r="F107" s="0"/>
+      <c r="H107" s="12"/>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0"/>
+      <c r="B113" s="0"/>
+      <c r="C113" s="0"/>
+      <c r="D113" s="0"/>
+      <c r="E113" s="0"/>
+      <c r="F113" s="0"/>
+      <c r="G113" s="0"/>
+      <c r="H113" s="0"/>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D50" r:id="rId1" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ without a body or an auth header"/>
-    <hyperlink ref="D51" r:id="rId2" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded id”, &quot;passwo"/>
-    <hyperlink ref="D52" r:id="rId3" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ without a body or an s_featured"/>
-    <hyperlink ref="D53" r:id="rId4" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded i” "/>
-    <hyperlink ref="D71" r:id="rId5" display="http://localhost:90/api/create_product/"/>
-    <hyperlink ref="D72" r:id="rId6" display="http://localhost:90/api/create_product/"/>
-    <hyperlink ref="D73" r:id="rId7" display="http://localhost:90/api/create_product/"/>
-    <hyperlink ref="D74" r:id="rId8" display="http://localhost:90/api/create_product/"/>
-    <hyperlink ref="D75" r:id="rId9" display="http://localhost:90/api/create_product/"/>
-    <hyperlink ref="D83" r:id="rId10" display="https://www.roysshack.hu/create_post"/>
-    <hyperlink ref="D84" r:id="rId11" display="https://www.roysshack.hu/create_post"/>
-    <hyperlink ref="D85" r:id="rId12" display="https://www.roysshack.hu/create_post"/>
-    <hyperlink ref="D86" r:id="rId13" display="https://www.roysshack.hu/create_post"/>
-    <hyperlink ref="D87" r:id="rId14" display="https://www.roysshack.hu/create_post"/>
+    <hyperlink ref="C50" r:id="rId1" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ without a body or an auth header"/>
+    <hyperlink ref="C51" r:id="rId2" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded id”, &quot;passwo"/>
+    <hyperlink ref="C52" r:id="rId3" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ without a body or an s_featured"/>
+    <hyperlink ref="C53" r:id="rId4" display="1. Open postman 2. Send a request to  http://localhost:90/api/get_all_product_categories/ with the body  „ {    &quot;id&quot;: &quot;&lt;b64encoded i” "/>
+    <hyperlink ref="C71" r:id="rId5" display="1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  &quot;admin_id&quot;: &quot;&lt;b64 encoded admin user {   &quot;user_id&quot;: &quot;&lt;base64 enc. id of admin&gt;&quot;,    &quot;session_token&quot;: &quot;&lt;base64 enc. session token of admin&gt;&quot;,    &quot;name_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;price_huf&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;times_ordered&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;stock&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;sale_percentage&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;description_preview_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;description_preview_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_preview_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;manufacturer&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;brand&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;rating&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;sku&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;active_ingredients&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;packaging_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;thumbnail_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;, &quot;featured&quot;:&quot;&lt;b64 enc. Int&gt;&quot;  }"/>
+    <hyperlink ref="C72" r:id="rId6" display="1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  &quot;admin_id&quot;: &quot;&lt;b64 encoded admin user {   &quot;user_id&quot;: &quot;&lt;base64 encNOT . id of admin&gt;&quot;,    &quot;session_token&quot;: &quot;&lt;base64 enc. session token of admin&gt;&quot;,    &quot;name_de&quot;:&quot;&lt;b64 enc. Strina NOT g&gt;&quot;,  user   &quot;description_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;price_huf&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;times_ordered&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;stock&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;sale_percentage&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;description_preview_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;description_preview_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_preview_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;manufacturer&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;brand&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;rating&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;sku&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;active_ingredients&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;packaging_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;thumbnail_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;, &quot;featured&quot;:&quot;&lt;b64 enc. Int&gt;&quot;  }"/>
+    <hyperlink ref="C73" r:id="rId7" display="1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  &quot;admin_id&quot;: &quot;&lt;b64 encoded admin user {   &quot;user_id&quot;: &quot;&lt;base64 enc. id of admin&gt;&quot;,    &quot;session_token&quot;: &quot;&lt;base64 enc. INCORRECT session token of admin&gt;&quot;,    &quot;name_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;price_huf&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;times_ordered&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;stock&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;sale_percentage&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;description_preview_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;description_preview_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_preview_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;manufacturer&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;brand&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;rating&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;sku&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;active_ingredients&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;packaging_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;thumbnail_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;, &quot;featured&quot;:&quot;&lt;b64 enc. Int&gt;&quot;  }"/>
+    <hyperlink ref="C74" r:id="rId8" display="1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  &quot;admin_id&quot;: &quot;&lt;b64 encoded admin user {   &quot;user_id&quot;: &quot;&lt;base64 enc. id of admin&gt;&quot;,    &quot;session_token&quot;: &quot;&lt;base64 enc. session token of admin&gt;&quot;,    &quot;name_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;price_huf&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;times_ordered&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;stock&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;sale_percentage&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;description_preview_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;description_preview_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_preview_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;manufacturer&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;brand&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;rating&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;sku&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;active_ingredients&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;packaging_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;thumbnail_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;, &quot;featured&quot;:&quot;&lt;b64 enc. Int&gt;&quot;  }, and no header"/>
+    <hyperlink ref="C75" r:id="rId9" display="1. Open postman 2. Send a request to  http://localhost:90/api/create_product/ with the body {  &quot;admin_id&quot;: &quot;&lt;b64 encoded admin user {   &quot;user_id&quot;: &quot;&lt;base64 enc. id of admin&gt;&quot;,    &quot;session_token&quot;: &quot;&lt;base64 enc. session token of admin&gt;&quot;,    &quot;name_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;price_huf&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;times_ordered&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;stock&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;sale_percentage&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;description_preview_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;name_en&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,     &quot;description_preview_hu&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;description_preview_de&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;manufacturer&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;brand&quot;:&quot;&lt;b64 enc. string&gt;&quot;,  &quot;rating&quot;:&quot;&lt;b64 enc. int&gt;&quot;,  &quot;sku&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;active_ingredients&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;packaging_en&quot;:&quot;&lt;b64 enc. String&gt;&quot;  }"/>
+    <hyperlink ref="C83" r:id="rId10" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. string&gt;&quot; }   "/>
+    <hyperlink ref="C84" r:id="rId11" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of NON-ADMIN user&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of NON-ADMIN user&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. string&gt;&quot; }   "/>
+    <hyperlink ref="C85" r:id="rId12" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. INCORRECT session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. string&gt;&quot; }   "/>
+    <hyperlink ref="C86" r:id="rId13" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. String&gt;&quot; }, and no auth header"/>
+    <hyperlink ref="C87" r:id="rId14" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. Int&gt;&quot; }   "/>
+    <hyperlink ref="C102" r:id="rId15" display="https://www.roysshack.hu/update_stock_admin"/>
+    <hyperlink ref="C103" r:id="rId16" display="https://www.roysshack.hu/update_stock_admin"/>
+    <hyperlink ref="C104" r:id="rId17" display="https://www.roysshack.hu/update_stock_admin"/>
+    <hyperlink ref="C105" r:id="rId18" display="https://www.roysshack.hu/update_stock_admin"/>
+    <hyperlink ref="C106" r:id="rId19" display="https://www.roysshack.hu/update_stock_admin"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/backend tests.xlsx
+++ b/backend tests.xlsx
@@ -1473,7 +1473,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1524,6 +1524,10 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4229,15 +4233,15 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0"/>
-      <c r="B101" s="0"/>
-      <c r="C101" s="0"/>
-      <c r="D101" s="0"/>
-      <c r="E101" s="0"/>
-      <c r="F101" s="0"/>
-      <c r="G101" s="0"/>
-      <c r="H101" s="0"/>
-      <c r="I101" s="0"/>
+      <c r="A101" s="13"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
@@ -4264,7 +4268,7 @@
       <c r="H102" s="12" t="n">
         <v>46105</v>
       </c>
-      <c r="I102" s="0"/>
+      <c r="I102" s="13"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
@@ -4291,7 +4295,7 @@
       <c r="H103" s="12" t="n">
         <v>46105</v>
       </c>
-      <c r="I103" s="0"/>
+      <c r="I103" s="13"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
@@ -4318,7 +4322,7 @@
       <c r="H104" s="12" t="n">
         <v>46105</v>
       </c>
-      <c r="I104" s="0"/>
+      <c r="I104" s="13"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
@@ -4374,7 +4378,7 @@
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="10"/>
-      <c r="F107" s="0"/>
+      <c r="F107" s="13"/>
       <c r="H107" s="12"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4508,14 +4512,14 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0"/>
-      <c r="B113" s="0"/>
-      <c r="C113" s="0"/>
-      <c r="D113" s="0"/>
-      <c r="E113" s="0"/>
-      <c r="F113" s="0"/>
-      <c r="G113" s="0"/>
-      <c r="H113" s="0"/>
+      <c r="A113" s="13"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
@@ -4587,11 +4591,11 @@
     <hyperlink ref="C85" r:id="rId12" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. INCORRECT session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. string&gt;&quot; }   "/>
     <hyperlink ref="C86" r:id="rId13" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;is_featured&quot;:&quot;&lt;b64 enc. int (0,1)&gt;&quot;,    &quot;tags&quot;:&quot;&lt;b64 enc. String&gt;&quot; }, and no auth header"/>
     <hyperlink ref="C87" r:id="rId14" display="1. Open postman 2. Send a request to https://www.roysshack.hu/create_post with the body: {   &quot;user_id&quot;: &quot;&lt;b64 enc. id of admin&gt;&quot;,   &quot;session_token&quot;: &quot;&quot;&lt;b64 enc. session token of admin&gt;&quot;,   &quot;title&quot;:&quot;&quot;&lt;b64 enc. string&gt;&quot;,    &quot;content&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;image_url&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;category_id&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;slug&quot;:&quot;&lt;b64 enc. string&gt;&quot;,   &quot;except&quot;:&quot;&lt;b64 enc. string&gt;&quot;,    &quot;status&quot;:&quot;&lt;b64 enc. string (hidden, draft, published, archived)&gt;&quot;,   &quot;views&quot;:&quot;&lt;b64 enc. int&gt;&quot;,    &quot;likes&quot;:&quot;&lt;b64 enc. int&gt;&quot;,   &quot;comment_count&quot;:&quot;&lt;b64 enc. Int&gt;&quot; }   "/>
-    <hyperlink ref="C102" r:id="rId15" display="https://www.roysshack.hu/update_stock_admin"/>
-    <hyperlink ref="C103" r:id="rId16" display="https://www.roysshack.hu/update_stock_admin"/>
-    <hyperlink ref="C104" r:id="rId17" display="https://www.roysshack.hu/update_stock_admin"/>
-    <hyperlink ref="C105" r:id="rId18" display="https://www.roysshack.hu/update_stock_admin"/>
-    <hyperlink ref="C106" r:id="rId19" display="https://www.roysshack.hu/update_stock_admin"/>
+    <hyperlink ref="C102" r:id="rId15" display="1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  &quot;user_id&quot;:&quot;&lt;b64 enc. id of user&gt;&quot;, &quot;session_token&quot;:&quot;&lt;b64 enc. session token of user&gt;&quot;, &quot;post_id&quot;:&quot;&lt;b64 enc. id of post&gt;&quot; }"/>
+    <hyperlink ref="C103" r:id="rId16" display="1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  &quot;user_id&quot;:&quot;&lt;b64 enc. id of user&gt;&quot;, &quot;session_token&quot;:&quot;&lt;b64 enc. session token of user&gt;&quot;, &quot;post_id&quot;:&quot;&lt;b64 enc. id of post&gt;&quot; }"/>
+    <hyperlink ref="C104" r:id="rId17" display="1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  &quot;user_id&quot;:&quot;&lt;b64 enc. id of user&gt;&quot;, &quot;session_token&quot;:&quot;&lt;b64 enc. INCORRECT session token of user&gt;&quot;, &quot;post_id&quot;:&quot;&lt;b64 enc. id of post&gt;&quot; }"/>
+    <hyperlink ref="C105" r:id="rId18" display="1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  &quot;user_id&quot;:&quot;&lt;b64 enc. id of user&gt;&quot;, &quot;session_token&quot;:&quot;&lt;b64 enc. session token of user&gt;&quot;, &quot;post_id&quot;:&quot;&lt;b64 enc. id of post&gt;&quot; }, and no auth header"/>
+    <hyperlink ref="C106" r:id="rId19" display="1. Open postman 2. Send a request to https://www.roysshack.hu/update_stock_admin with the body {  &quot;user_id&quot;:&quot;&lt;b64 enc. id of user&gt;&quot;, &quot;session_token&quot;:&quot;&lt;b64 enc. session token of user&gt;&quot;, &quot;post_id&quot;:"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
